--- a/AAII_Financials/Quarterly/NCI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NCI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
   <si>
     <t>NCI</t>
   </si>
@@ -1005,10 +1005,10 @@
         <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -1200,10 +1200,10 @@
         <v>400</v>
       </c>
       <c r="H21" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="I21" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="J21" s="3">
         <v>200</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
@@ -2046,11 +2046,11 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>4</v>
+      <c r="D45" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3800</v>
       </c>
       <c r="F45" s="3">
         <v>0</v>
@@ -2059,10 +2059,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="J45" s="3">
         <v>6800</v>
@@ -2573,10 +2573,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E59" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F59" s="3">
         <v>500</v>
@@ -3431,11 +3431,11 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>4</v>
+      <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -3689,11 +3689,11 @@
       <c r="G89" s="3">
         <v>200</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>4</v>
+      <c r="H89" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I89" s="3">
+        <v>1400</v>
       </c>
       <c r="J89" s="3">
         <v>-1400</v>
@@ -3747,11 +3747,11 @@
       <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>4</v>
+      <c r="H91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-200</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
@@ -3870,11 +3870,11 @@
       <c r="G94" s="3">
         <v>-400</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
+      <c r="H94" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-1200</v>
       </c>
       <c r="J94" s="3">
         <v>-100</v>
@@ -4092,11 +4092,11 @@
       <c r="G100" s="3">
         <v>-300</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>4</v>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
       </c>
       <c r="J100" s="3">
         <v>1400</v>
@@ -4121,11 +4121,11 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>4</v>
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>4</v>
@@ -4175,10 +4175,10 @@
         <v>-500</v>
       </c>
       <c r="H102" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I102" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J102" s="3">
         <v>-100</v>
